--- a/InputData/io-model/BEbIC/BAU Employment by ISIC Code.xlsx
+++ b/InputData/io-model/BEbIC/BAU Employment by ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shigu\Documents\_swj\_Talanoa\CPSA Fletcher\dados\InputData (BR) 2024\d14 io-model\BEbIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/io-model/BEbIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7789C51B-C64F-4997-9374-EC6B9351C578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05572989-870E-B44E-8100-54FC2E252392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3744" windowWidth="17280" windowHeight="9900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3740" windowWidth="17280" windowHeight="9900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1691,20 +1691,29 @@
     <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1733,23 +1742,14 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1765,7 +1765,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{3ADF3FF5-E4D2-4BC8-9960-7408DCCB591E}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{0C79E43D-D088-43AF-AD66-AC2EF134DE21}"/>
@@ -2051,9 +2051,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="77.5546875" customWidth="1"/>
+    <col min="2" max="2" width="77.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2157,17 +2157,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CBC0E5-825F-4023-A65B-FD98CE5167C8}">
   <dimension ref="A1:BE74"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="2.44140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="2.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="53" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="9.5" style="6" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.5" style="6" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.109375" style="6"/>
+    <col min="58" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" hidden="1">
@@ -2179,554 +2179,554 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="34.799999999999997">
+    <row r="2" spans="1:57" ht="26">
       <c r="A2" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:57">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="78" t="s">
+      <c r="B3" s="83"/>
+      <c r="C3" s="93" t="s">
         <v>169</v>
       </c>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
-      <c r="AM3" s="79"/>
-      <c r="AN3" s="79"/>
-      <c r="AO3" s="79"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="79"/>
-      <c r="AR3" s="79"/>
-      <c r="AS3" s="79"/>
-      <c r="AT3" s="79"/>
-      <c r="AU3" s="79"/>
-      <c r="AV3" s="79"/>
-      <c r="AW3" s="79"/>
-      <c r="AX3" s="79"/>
-      <c r="AY3" s="79"/>
-      <c r="AZ3" s="79"/>
-      <c r="BA3" s="79"/>
-      <c r="BB3" s="79"/>
-      <c r="BC3" s="79"/>
-      <c r="BD3" s="79"/>
-      <c r="BE3" s="80"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="94"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="94"/>
+      <c r="V3" s="94"/>
+      <c r="W3" s="94"/>
+      <c r="X3" s="94"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
+      <c r="AB3" s="94"/>
+      <c r="AC3" s="94"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="94"/>
+      <c r="AI3" s="94"/>
+      <c r="AJ3" s="94"/>
+      <c r="AK3" s="94"/>
+      <c r="AL3" s="94"/>
+      <c r="AM3" s="94"/>
+      <c r="AN3" s="94"/>
+      <c r="AO3" s="94"/>
+      <c r="AP3" s="94"/>
+      <c r="AQ3" s="94"/>
+      <c r="AR3" s="94"/>
+      <c r="AS3" s="94"/>
+      <c r="AT3" s="94"/>
+      <c r="AU3" s="94"/>
+      <c r="AV3" s="94"/>
+      <c r="AW3" s="94"/>
+      <c r="AX3" s="94"/>
+      <c r="AY3" s="94"/>
+      <c r="AZ3" s="94"/>
+      <c r="BA3" s="94"/>
+      <c r="BB3" s="94"/>
+      <c r="BC3" s="94"/>
+      <c r="BD3" s="94"/>
+      <c r="BE3" s="95"/>
     </row>
     <row r="4" spans="1:57">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="82" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="81" t="s">
+      <c r="B4" s="83"/>
+      <c r="C4" s="84" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="82"/>
-      <c r="W4" s="82"/>
-      <c r="X4" s="82"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
-      <c r="AC4" s="82"/>
-      <c r="AD4" s="82"/>
-      <c r="AE4" s="82"/>
-      <c r="AF4" s="82"/>
-      <c r="AG4" s="82"/>
-      <c r="AH4" s="82"/>
-      <c r="AI4" s="82"/>
-      <c r="AJ4" s="82"/>
-      <c r="AK4" s="82"/>
-      <c r="AL4" s="82"/>
-      <c r="AM4" s="82"/>
-      <c r="AN4" s="82"/>
-      <c r="AO4" s="82"/>
-      <c r="AP4" s="82"/>
-      <c r="AQ4" s="82"/>
-      <c r="AR4" s="82"/>
-      <c r="AS4" s="82"/>
-      <c r="AT4" s="82"/>
-      <c r="AU4" s="82"/>
-      <c r="AV4" s="82"/>
-      <c r="AW4" s="82"/>
-      <c r="AX4" s="82"/>
-      <c r="AY4" s="82"/>
-      <c r="AZ4" s="82"/>
-      <c r="BA4" s="82"/>
-      <c r="BB4" s="82"/>
-      <c r="BC4" s="82"/>
-      <c r="BD4" s="82"/>
-      <c r="BE4" s="83"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="85"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="85"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
+      <c r="AH4" s="85"/>
+      <c r="AI4" s="85"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="85"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
+      <c r="AR4" s="85"/>
+      <c r="AS4" s="85"/>
+      <c r="AT4" s="85"/>
+      <c r="AU4" s="85"/>
+      <c r="AV4" s="85"/>
+      <c r="AW4" s="85"/>
+      <c r="AX4" s="85"/>
+      <c r="AY4" s="85"/>
+      <c r="AZ4" s="85"/>
+      <c r="BA4" s="85"/>
+      <c r="BB4" s="85"/>
+      <c r="BC4" s="85"/>
+      <c r="BD4" s="85"/>
+      <c r="BE4" s="86"/>
     </row>
     <row r="5" spans="1:57">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="81" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="82"/>
-      <c r="Y5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="82"/>
-      <c r="AD5" s="82"/>
-      <c r="AE5" s="82"/>
-      <c r="AF5" s="82"/>
-      <c r="AG5" s="82"/>
-      <c r="AH5" s="82"/>
-      <c r="AI5" s="82"/>
-      <c r="AJ5" s="82"/>
-      <c r="AK5" s="82"/>
-      <c r="AL5" s="82"/>
-      <c r="AM5" s="82"/>
-      <c r="AN5" s="82"/>
-      <c r="AO5" s="82"/>
-      <c r="AP5" s="82"/>
-      <c r="AQ5" s="82"/>
-      <c r="AR5" s="82"/>
-      <c r="AS5" s="82"/>
-      <c r="AT5" s="82"/>
-      <c r="AU5" s="82"/>
-      <c r="AV5" s="82"/>
-      <c r="AW5" s="82"/>
-      <c r="AX5" s="82"/>
-      <c r="AY5" s="82"/>
-      <c r="AZ5" s="82"/>
-      <c r="BA5" s="82"/>
-      <c r="BB5" s="82"/>
-      <c r="BC5" s="82"/>
-      <c r="BD5" s="82"/>
-      <c r="BE5" s="83"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="85"/>
+      <c r="AE5" s="85"/>
+      <c r="AF5" s="85"/>
+      <c r="AG5" s="85"/>
+      <c r="AH5" s="85"/>
+      <c r="AI5" s="85"/>
+      <c r="AJ5" s="85"/>
+      <c r="AK5" s="85"/>
+      <c r="AL5" s="85"/>
+      <c r="AM5" s="85"/>
+      <c r="AN5" s="85"/>
+      <c r="AO5" s="85"/>
+      <c r="AP5" s="85"/>
+      <c r="AQ5" s="85"/>
+      <c r="AR5" s="85"/>
+      <c r="AS5" s="85"/>
+      <c r="AT5" s="85"/>
+      <c r="AU5" s="85"/>
+      <c r="AV5" s="85"/>
+      <c r="AW5" s="85"/>
+      <c r="AX5" s="85"/>
+      <c r="AY5" s="85"/>
+      <c r="AZ5" s="85"/>
+      <c r="BA5" s="85"/>
+      <c r="BB5" s="85"/>
+      <c r="BC5" s="85"/>
+      <c r="BD5" s="85"/>
+      <c r="BE5" s="86"/>
     </row>
     <row r="6" spans="1:57">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="83"/>
+      <c r="C6" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82"/>
-      <c r="Q6" s="82"/>
-      <c r="R6" s="82"/>
-      <c r="S6" s="82"/>
-      <c r="T6" s="82"/>
-      <c r="U6" s="82"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="82"/>
-      <c r="X6" s="82"/>
-      <c r="Y6" s="82"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="82"/>
-      <c r="AB6" s="82"/>
-      <c r="AC6" s="82"/>
-      <c r="AD6" s="82"/>
-      <c r="AE6" s="82"/>
-      <c r="AF6" s="82"/>
-      <c r="AG6" s="82"/>
-      <c r="AH6" s="82"/>
-      <c r="AI6" s="82"/>
-      <c r="AJ6" s="82"/>
-      <c r="AK6" s="82"/>
-      <c r="AL6" s="82"/>
-      <c r="AM6" s="82"/>
-      <c r="AN6" s="82"/>
-      <c r="AO6" s="82"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="82"/>
-      <c r="AR6" s="82"/>
-      <c r="AS6" s="82"/>
-      <c r="AT6" s="82"/>
-      <c r="AU6" s="82"/>
-      <c r="AV6" s="82"/>
-      <c r="AW6" s="82"/>
-      <c r="AX6" s="82"/>
-      <c r="AY6" s="82"/>
-      <c r="AZ6" s="82"/>
-      <c r="BA6" s="82"/>
-      <c r="BB6" s="82"/>
-      <c r="BC6" s="82"/>
-      <c r="BD6" s="82"/>
-      <c r="BE6" s="83"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="85"/>
+      <c r="U6" s="85"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="85"/>
+      <c r="X6" s="85"/>
+      <c r="Y6" s="85"/>
+      <c r="Z6" s="85"/>
+      <c r="AA6" s="85"/>
+      <c r="AB6" s="85"/>
+      <c r="AC6" s="85"/>
+      <c r="AD6" s="85"/>
+      <c r="AE6" s="85"/>
+      <c r="AF6" s="85"/>
+      <c r="AG6" s="85"/>
+      <c r="AH6" s="85"/>
+      <c r="AI6" s="85"/>
+      <c r="AJ6" s="85"/>
+      <c r="AK6" s="85"/>
+      <c r="AL6" s="85"/>
+      <c r="AM6" s="85"/>
+      <c r="AN6" s="85"/>
+      <c r="AO6" s="85"/>
+      <c r="AP6" s="85"/>
+      <c r="AQ6" s="85"/>
+      <c r="AR6" s="85"/>
+      <c r="AS6" s="85"/>
+      <c r="AT6" s="85"/>
+      <c r="AU6" s="85"/>
+      <c r="AV6" s="85"/>
+      <c r="AW6" s="85"/>
+      <c r="AX6" s="85"/>
+      <c r="AY6" s="85"/>
+      <c r="AZ6" s="85"/>
+      <c r="BA6" s="85"/>
+      <c r="BB6" s="85"/>
+      <c r="BC6" s="85"/>
+      <c r="BD6" s="85"/>
+      <c r="BE6" s="86"/>
     </row>
     <row r="7" spans="1:57">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="87" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="90" t="s">
+      <c r="B7" s="88"/>
+      <c r="C7" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="D7" s="93" t="s">
+      <c r="D7" s="76" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
-      <c r="S7" s="94"/>
-      <c r="T7" s="94"/>
-      <c r="U7" s="94"/>
-      <c r="V7" s="94"/>
-      <c r="W7" s="94"/>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="94"/>
-      <c r="Z7" s="94"/>
-      <c r="AA7" s="94"/>
-      <c r="AB7" s="94"/>
-      <c r="AC7" s="94"/>
-      <c r="AD7" s="94"/>
-      <c r="AE7" s="94"/>
-      <c r="AF7" s="94"/>
-      <c r="AG7" s="94"/>
-      <c r="AH7" s="94"/>
-      <c r="AI7" s="94"/>
-      <c r="AJ7" s="94"/>
-      <c r="AK7" s="94"/>
-      <c r="AL7" s="94"/>
-      <c r="AM7" s="94"/>
-      <c r="AN7" s="94"/>
-      <c r="AO7" s="94"/>
-      <c r="AP7" s="94"/>
-      <c r="AQ7" s="94"/>
-      <c r="AR7" s="94"/>
-      <c r="AS7" s="94"/>
-      <c r="AT7" s="94"/>
-      <c r="AU7" s="94"/>
-      <c r="AV7" s="94"/>
-      <c r="AW7" s="94"/>
-      <c r="AX7" s="94"/>
-      <c r="AY7" s="94"/>
-      <c r="AZ7" s="94"/>
-      <c r="BA7" s="94"/>
-      <c r="BB7" s="94"/>
-      <c r="BC7" s="94"/>
-      <c r="BD7" s="94"/>
-      <c r="BE7" s="95"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="81"/>
+      <c r="AB7" s="81"/>
+      <c r="AC7" s="81"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="81"/>
+      <c r="AF7" s="81"/>
+      <c r="AG7" s="81"/>
+      <c r="AH7" s="81"/>
+      <c r="AI7" s="81"/>
+      <c r="AJ7" s="81"/>
+      <c r="AK7" s="81"/>
+      <c r="AL7" s="81"/>
+      <c r="AM7" s="81"/>
+      <c r="AN7" s="81"/>
+      <c r="AO7" s="81"/>
+      <c r="AP7" s="81"/>
+      <c r="AQ7" s="81"/>
+      <c r="AR7" s="81"/>
+      <c r="AS7" s="81"/>
+      <c r="AT7" s="81"/>
+      <c r="AU7" s="81"/>
+      <c r="AV7" s="81"/>
+      <c r="AW7" s="81"/>
+      <c r="AX7" s="81"/>
+      <c r="AY7" s="81"/>
+      <c r="AZ7" s="81"/>
+      <c r="BA7" s="81"/>
+      <c r="BB7" s="81"/>
+      <c r="BC7" s="81"/>
+      <c r="BD7" s="81"/>
+      <c r="BE7" s="77"/>
     </row>
     <row r="8" spans="1:57">
-      <c r="A8" s="86"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="90" t="s">
+      <c r="A8" s="89"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="78" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="90" t="s">
+      <c r="E8" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="93" t="s">
+      <c r="F8" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="G8" s="94"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="90" t="s">
+      <c r="G8" s="81"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="J8" s="93" t="s">
+      <c r="J8" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
-      <c r="S8" s="94"/>
-      <c r="T8" s="94"/>
-      <c r="U8" s="94"/>
-      <c r="V8" s="94"/>
-      <c r="W8" s="94"/>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="94"/>
-      <c r="Z8" s="94"/>
-      <c r="AA8" s="94"/>
-      <c r="AB8" s="94"/>
-      <c r="AC8" s="94"/>
-      <c r="AD8" s="95"/>
-      <c r="AE8" s="90" t="s">
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="81"/>
+      <c r="X8" s="81"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="81"/>
+      <c r="AB8" s="81"/>
+      <c r="AC8" s="81"/>
+      <c r="AD8" s="77"/>
+      <c r="AE8" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="AF8" s="90" t="s">
+      <c r="AF8" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="AG8" s="90" t="s">
+      <c r="AG8" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="AH8" s="93" t="s">
+      <c r="AH8" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="AI8" s="94"/>
-      <c r="AJ8" s="94"/>
-      <c r="AK8" s="94"/>
-      <c r="AL8" s="94"/>
-      <c r="AM8" s="94"/>
-      <c r="AN8" s="94"/>
-      <c r="AO8" s="94"/>
-      <c r="AP8" s="94"/>
-      <c r="AQ8" s="94"/>
-      <c r="AR8" s="95"/>
-      <c r="AS8" s="90" t="s">
+      <c r="AI8" s="81"/>
+      <c r="AJ8" s="81"/>
+      <c r="AK8" s="81"/>
+      <c r="AL8" s="81"/>
+      <c r="AM8" s="81"/>
+      <c r="AN8" s="81"/>
+      <c r="AO8" s="81"/>
+      <c r="AP8" s="81"/>
+      <c r="AQ8" s="81"/>
+      <c r="AR8" s="77"/>
+      <c r="AS8" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="AT8" s="93" t="s">
+      <c r="AT8" s="76" t="s">
         <v>157</v>
       </c>
-      <c r="AU8" s="94"/>
-      <c r="AV8" s="94"/>
-      <c r="AW8" s="94"/>
-      <c r="AX8" s="94"/>
-      <c r="AY8" s="94"/>
-      <c r="AZ8" s="95"/>
-      <c r="BA8" s="90" t="s">
+      <c r="AU8" s="81"/>
+      <c r="AV8" s="81"/>
+      <c r="AW8" s="81"/>
+      <c r="AX8" s="81"/>
+      <c r="AY8" s="81"/>
+      <c r="AZ8" s="77"/>
+      <c r="BA8" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="BB8" s="90" t="s">
+      <c r="BB8" s="78" t="s">
         <v>155</v>
       </c>
-      <c r="BC8" s="90" t="s">
+      <c r="BC8" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="BD8" s="90" t="s">
+      <c r="BD8" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="BE8" s="90" t="s">
+      <c r="BE8" s="78" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:57">
-      <c r="A9" s="86"/>
-      <c r="B9" s="87"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="90" t="s">
+      <c r="A9" s="89"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="G9" s="90" t="s">
+      <c r="G9" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="H9" s="90" t="s">
+      <c r="H9" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="I9" s="91"/>
-      <c r="J9" s="90" t="s">
+      <c r="I9" s="80"/>
+      <c r="J9" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="K9" s="90" t="s">
+      <c r="K9" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="L9" s="90" t="s">
+      <c r="L9" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="M9" s="93" t="s">
+      <c r="M9" s="76" t="s">
         <v>146</v>
       </c>
-      <c r="N9" s="95"/>
-      <c r="O9" s="90" t="s">
+      <c r="N9" s="77"/>
+      <c r="O9" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="P9" s="93" t="s">
+      <c r="P9" s="76" t="s">
         <v>145</v>
       </c>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
-      <c r="S9" s="95"/>
-      <c r="T9" s="90" t="s">
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="U9" s="93" t="s">
+      <c r="U9" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="V9" s="95"/>
-      <c r="W9" s="90" t="s">
+      <c r="V9" s="77"/>
+      <c r="W9" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="X9" s="93" t="s">
+      <c r="X9" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="Y9" s="95"/>
-      <c r="Z9" s="90" t="s">
+      <c r="Y9" s="77"/>
+      <c r="Z9" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="AA9" s="90" t="s">
+      <c r="AA9" s="78" t="s">
         <v>141</v>
       </c>
-      <c r="AB9" s="93" t="s">
+      <c r="AB9" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="AC9" s="95"/>
-      <c r="AD9" s="90" t="s">
+      <c r="AC9" s="77"/>
+      <c r="AD9" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="AE9" s="91"/>
-      <c r="AF9" s="91"/>
-      <c r="AG9" s="91"/>
-      <c r="AH9" s="90" t="s">
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="80"/>
+      <c r="AG9" s="80"/>
+      <c r="AH9" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="AI9" s="93" t="s">
+      <c r="AI9" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="AJ9" s="94"/>
-      <c r="AK9" s="95"/>
-      <c r="AL9" s="90" t="s">
+      <c r="AJ9" s="81"/>
+      <c r="AK9" s="77"/>
+      <c r="AL9" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="AM9" s="93" t="s">
+      <c r="AM9" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="AN9" s="94"/>
-      <c r="AO9" s="95"/>
-      <c r="AP9" s="90" t="s">
+      <c r="AN9" s="81"/>
+      <c r="AO9" s="77"/>
+      <c r="AP9" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="AQ9" s="90" t="s">
+      <c r="AQ9" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="AR9" s="90" t="s">
+      <c r="AR9" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="AS9" s="91"/>
-      <c r="AT9" s="90" t="s">
+      <c r="AS9" s="80"/>
+      <c r="AT9" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="AU9" s="93" t="s">
+      <c r="AU9" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="AV9" s="94"/>
-      <c r="AW9" s="95"/>
-      <c r="AX9" s="90" t="s">
+      <c r="AV9" s="81"/>
+      <c r="AW9" s="77"/>
+      <c r="AX9" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="AY9" s="93" t="s">
+      <c r="AY9" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="AZ9" s="95"/>
-      <c r="BA9" s="91"/>
-      <c r="BB9" s="91"/>
-      <c r="BC9" s="91"/>
-      <c r="BD9" s="91"/>
-      <c r="BE9" s="91"/>
-    </row>
-    <row r="10" spans="1:57" ht="91.8">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
+      <c r="AZ9" s="77"/>
+      <c r="BA9" s="80"/>
+      <c r="BB9" s="80"/>
+      <c r="BC9" s="80"/>
+      <c r="BD9" s="80"/>
+      <c r="BE9" s="80"/>
+    </row>
+    <row r="10" spans="1:57" ht="108">
+      <c r="A10" s="91"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
       <c r="M10" s="8" t="s">
         <v>132</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="O10" s="92"/>
+      <c r="O10" s="79"/>
       <c r="P10" s="8" t="s">
         <v>130</v>
       </c>
@@ -2739,33 +2739,33 @@
       <c r="S10" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="92"/>
+      <c r="T10" s="79"/>
       <c r="U10" s="8" t="s">
         <v>126</v>
       </c>
       <c r="V10" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="W10" s="92"/>
+      <c r="W10" s="79"/>
       <c r="X10" s="8" t="s">
         <v>124</v>
       </c>
       <c r="Y10" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="Z10" s="92"/>
-      <c r="AA10" s="92"/>
+      <c r="Z10" s="79"/>
+      <c r="AA10" s="79"/>
       <c r="AB10" s="8" t="s">
         <v>122</v>
       </c>
       <c r="AC10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AD10" s="92"/>
-      <c r="AE10" s="92"/>
-      <c r="AF10" s="92"/>
-      <c r="AG10" s="92"/>
-      <c r="AH10" s="92"/>
+      <c r="AD10" s="79"/>
+      <c r="AE10" s="79"/>
+      <c r="AF10" s="79"/>
+      <c r="AG10" s="79"/>
+      <c r="AH10" s="79"/>
       <c r="AI10" s="8" t="s">
         <v>120</v>
       </c>
@@ -2775,7 +2775,7 @@
       <c r="AK10" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="AL10" s="92"/>
+      <c r="AL10" s="79"/>
       <c r="AM10" s="8" t="s">
         <v>117</v>
       </c>
@@ -2785,11 +2785,11 @@
       <c r="AO10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="AP10" s="92"/>
-      <c r="AQ10" s="92"/>
-      <c r="AR10" s="92"/>
-      <c r="AS10" s="92"/>
-      <c r="AT10" s="92"/>
+      <c r="AP10" s="79"/>
+      <c r="AQ10" s="79"/>
+      <c r="AR10" s="79"/>
+      <c r="AS10" s="79"/>
+      <c r="AT10" s="79"/>
       <c r="AU10" s="8" t="s">
         <v>114</v>
       </c>
@@ -2799,20 +2799,20 @@
       <c r="AW10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AX10" s="92"/>
+      <c r="AX10" s="79"/>
       <c r="AY10" s="8" t="s">
         <v>111</v>
       </c>
       <c r="AZ10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="BA10" s="92"/>
-      <c r="BB10" s="92"/>
-      <c r="BC10" s="92"/>
-      <c r="BD10" s="92"/>
-      <c r="BE10" s="92"/>
-    </row>
-    <row r="11" spans="1:57" ht="13.8">
+      <c r="BA10" s="79"/>
+      <c r="BB10" s="79"/>
+      <c r="BC10" s="79"/>
+      <c r="BD10" s="79"/>
+      <c r="BE10" s="79"/>
+    </row>
+    <row r="11" spans="1:57" ht="14">
       <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:57" ht="13.8">
+    <row r="12" spans="1:57" ht="14">
       <c r="A12" s="11" t="s">
         <v>109</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>20470.599999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:57" ht="13.8">
+    <row r="13" spans="1:57" ht="14">
       <c r="A13" s="11" t="s">
         <v>108</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>445.1</v>
       </c>
     </row>
-    <row r="14" spans="1:57" ht="13.8">
+    <row r="14" spans="1:57" ht="14">
       <c r="A14" s="11" t="s">
         <v>107</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>133.4</v>
       </c>
     </row>
-    <row r="15" spans="1:57" ht="13.8">
+    <row r="15" spans="1:57" ht="14">
       <c r="A15" s="11" t="s">
         <v>106</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="16" spans="1:57" ht="13.8">
+    <row r="16" spans="1:57" ht="14">
       <c r="A16" s="11" t="s">
         <v>105</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>684.1</v>
       </c>
     </row>
-    <row r="17" spans="1:57" ht="13.8">
+    <row r="17" spans="1:57" ht="14">
       <c r="A17" s="11" t="s">
         <v>104</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>141.80000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:57" ht="13.8">
+    <row r="18" spans="1:57" ht="14">
       <c r="A18" s="11" t="s">
         <v>103</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>182.6</v>
       </c>
     </row>
-    <row r="19" spans="1:57" ht="13.8">
+    <row r="19" spans="1:57" ht="14">
       <c r="A19" s="11" t="s">
         <v>102</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>116.2</v>
       </c>
     </row>
-    <row r="20" spans="1:57" ht="13.8">
+    <row r="20" spans="1:57" ht="14">
       <c r="A20" s="11" t="s">
         <v>101</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:57" ht="13.8">
+    <row r="21" spans="1:57" ht="14">
       <c r="A21" s="11" t="s">
         <v>100</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:57" ht="13.8">
+    <row r="22" spans="1:57" ht="14">
       <c r="A22" s="11" t="s">
         <v>99</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>913.2</v>
       </c>
     </row>
-    <row r="23" spans="1:57" ht="13.8">
+    <row r="23" spans="1:57" ht="14">
       <c r="A23" s="11" t="s">
         <v>98</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="24" spans="1:57" ht="13.8">
+    <row r="24" spans="1:57" ht="14">
       <c r="A24" s="11" t="s">
         <v>97</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="25" spans="1:57" ht="13.8">
+    <row r="25" spans="1:57" ht="14">
       <c r="A25" s="11" t="s">
         <v>96</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>189.2</v>
       </c>
     </row>
-    <row r="26" spans="1:57" ht="13.8">
+    <row r="26" spans="1:57" ht="14">
       <c r="A26" s="11" t="s">
         <v>95</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="27" spans="1:57" ht="13.8">
+    <row r="27" spans="1:57" ht="14">
       <c r="A27" s="11" t="s">
         <v>94</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="28" spans="1:57" ht="13.8">
+    <row r="28" spans="1:57" ht="14">
       <c r="A28" s="15" t="s">
         <v>93</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>246.1</v>
       </c>
     </row>
-    <row r="29" spans="1:57" ht="13.8">
+    <row r="29" spans="1:57" ht="14">
       <c r="A29" s="11" t="s">
         <v>92</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>688.4</v>
       </c>
     </row>
-    <row r="30" spans="1:57" ht="13.8">
+    <row r="30" spans="1:57" ht="14">
       <c r="A30" s="11" t="s">
         <v>91</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="31" spans="1:57" ht="13.8">
+    <row r="31" spans="1:57" ht="14">
       <c r="A31" s="11" t="s">
         <v>90</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>1341.5</v>
       </c>
     </row>
-    <row r="32" spans="1:57" ht="13.8">
+    <row r="32" spans="1:57" ht="14">
       <c r="A32" s="11" t="s">
         <v>89</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="33" spans="1:57" ht="13.8">
+    <row r="33" spans="1:57" ht="14">
       <c r="A33" s="11" t="s">
         <v>88</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="34" spans="1:57" ht="13.8">
+    <row r="34" spans="1:57" ht="14">
       <c r="A34" s="11" t="s">
         <v>87</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="35" spans="1:57" ht="13.8">
+    <row r="35" spans="1:57" ht="14">
       <c r="A35" s="11" t="s">
         <v>86</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>860.7</v>
       </c>
     </row>
-    <row r="36" spans="1:57" ht="13.8">
+    <row r="36" spans="1:57" ht="14">
       <c r="A36" s="11" t="s">
         <v>85</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:57" ht="13.8">
+    <row r="37" spans="1:57" ht="14">
       <c r="A37" s="11" t="s">
         <v>84</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="38" spans="1:57" ht="13.8">
+    <row r="38" spans="1:57" ht="14">
       <c r="A38" s="11" t="s">
         <v>83</v>
       </c>
@@ -7656,7 +7656,7 @@
         <v>101.7</v>
       </c>
     </row>
-    <row r="39" spans="1:57" ht="13.8">
+    <row r="39" spans="1:57" ht="14">
       <c r="A39" s="11" t="s">
         <v>82</v>
       </c>
@@ -7829,7 +7829,7 @@
         <v>460.1</v>
       </c>
     </row>
-    <row r="40" spans="1:57" ht="13.8">
+    <row r="40" spans="1:57" ht="14">
       <c r="A40" s="11" t="s">
         <v>81</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="41" spans="1:57" ht="13.8">
+    <row r="41" spans="1:57" ht="14">
       <c r="A41" s="11" t="s">
         <v>80</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>75.599999999999994</v>
       </c>
     </row>
-    <row r="42" spans="1:57" ht="13.8">
+    <row r="42" spans="1:57" ht="14">
       <c r="A42" s="11" t="s">
         <v>79</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="43" spans="1:57" ht="13.8">
+    <row r="43" spans="1:57" ht="14">
       <c r="A43" s="11" t="s">
         <v>78</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>519.4</v>
       </c>
     </row>
-    <row r="44" spans="1:57" ht="13.8">
+    <row r="44" spans="1:57" ht="14">
       <c r="A44" s="11" t="s">
         <v>77</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:57" ht="13.8">
+    <row r="45" spans="1:57" ht="14">
       <c r="A45" s="11" t="s">
         <v>76</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>265.89999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:57" ht="13.8">
+    <row r="46" spans="1:57" ht="14">
       <c r="A46" s="11" t="s">
         <v>75</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>295.3</v>
       </c>
     </row>
-    <row r="47" spans="1:57" ht="13.8">
+    <row r="47" spans="1:57" ht="14">
       <c r="A47" s="11" t="s">
         <v>74</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>1424.4</v>
       </c>
     </row>
-    <row r="48" spans="1:57" ht="13.8">
+    <row r="48" spans="1:57" ht="14">
       <c r="A48" s="11" t="s">
         <v>5</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>6023</v>
       </c>
     </row>
-    <row r="49" spans="1:57" ht="20.399999999999999">
+    <row r="49" spans="1:57" ht="24">
       <c r="A49" s="11" t="s">
         <v>73</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>38973.9</v>
       </c>
     </row>
-    <row r="50" spans="1:57" ht="13.8">
+    <row r="50" spans="1:57" ht="14">
       <c r="A50" s="11" t="s">
         <v>72</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>392.4</v>
       </c>
     </row>
-    <row r="51" spans="1:57" ht="13.8">
+    <row r="51" spans="1:57" ht="14">
       <c r="A51" s="11" t="s">
         <v>71</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>1493.8</v>
       </c>
     </row>
-    <row r="52" spans="1:57" ht="13.8">
+    <row r="52" spans="1:57" ht="14">
       <c r="A52" s="11" t="s">
         <v>70</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>97.4</v>
       </c>
     </row>
-    <row r="53" spans="1:57" ht="13.8">
+    <row r="53" spans="1:57" ht="14">
       <c r="A53" s="11" t="s">
         <v>69</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>28049.3</v>
       </c>
     </row>
-    <row r="54" spans="1:57" ht="13.8">
+    <row r="54" spans="1:57" ht="14">
       <c r="A54" s="11" t="s">
         <v>68</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>854.1</v>
       </c>
     </row>
-    <row r="55" spans="1:57" ht="13.8">
+    <row r="55" spans="1:57" ht="14">
       <c r="A55" s="11" t="s">
         <v>67</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="56" spans="1:57" ht="13.8">
+    <row r="56" spans="1:57" ht="14">
       <c r="A56" s="11" t="s">
         <v>66</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="57" spans="1:57" ht="13.8">
+    <row r="57" spans="1:57" ht="14">
       <c r="A57" s="15" t="s">
         <v>65</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:57" ht="13.8">
+    <row r="58" spans="1:57" ht="14">
       <c r="A58" s="11" t="s">
         <v>64</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>4317.8</v>
       </c>
     </row>
-    <row r="59" spans="1:57" ht="13.8">
+    <row r="59" spans="1:57" ht="14">
       <c r="A59" s="11" t="s">
         <v>63</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>1050.0999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:57" ht="13.8">
+    <row r="60" spans="1:57" ht="14">
       <c r="A60" s="11" t="s">
         <v>62</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="61" spans="1:57" ht="13.8">
+    <row r="61" spans="1:57" ht="14">
       <c r="A61" s="11" t="s">
         <v>61</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>218.4</v>
       </c>
     </row>
-    <row r="62" spans="1:57" ht="13.8">
+    <row r="62" spans="1:57" ht="14">
       <c r="A62" s="11" t="s">
         <v>60</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="63" spans="1:57" ht="13.8">
+    <row r="63" spans="1:57" ht="14">
       <c r="A63" s="11" t="s">
         <v>59</v>
       </c>
@@ -11981,7 +11981,7 @@
         <v>112.1</v>
       </c>
     </row>
-    <row r="64" spans="1:57" ht="13.8">
+    <row r="64" spans="1:57" ht="14">
       <c r="A64" s="11" t="s">
         <v>58</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>313.8</v>
       </c>
     </row>
-    <row r="65" spans="1:57" ht="13.8">
+    <row r="65" spans="1:57" ht="14">
       <c r="A65" s="15" t="s">
         <v>57</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>31907.8</v>
       </c>
     </row>
-    <row r="66" spans="1:57" ht="20.399999999999999">
+    <row r="66" spans="1:57" ht="14">
       <c r="A66" s="15" t="s">
         <v>56</v>
       </c>
@@ -12500,7 +12500,7 @@
         <v>6406.6</v>
       </c>
     </row>
-    <row r="67" spans="1:57" ht="20.399999999999999">
+    <row r="67" spans="1:57" ht="14">
       <c r="A67" s="15" t="s">
         <v>55</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>7824.5</v>
       </c>
     </row>
-    <row r="68" spans="1:57" ht="13.8">
+    <row r="68" spans="1:57" ht="14">
       <c r="A68" s="15" t="s">
         <v>54</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>1417.9</v>
       </c>
     </row>
-    <row r="69" spans="1:57" ht="13.8">
+    <row r="69" spans="1:57" ht="14">
       <c r="A69" s="15" t="s">
         <v>53</v>
       </c>
@@ -13019,7 +13019,7 @@
         <v>4875.8</v>
       </c>
     </row>
-    <row r="70" spans="1:57" ht="13.8">
+    <row r="70" spans="1:57" ht="14">
       <c r="A70" s="15" t="s">
         <v>52</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>4651</v>
       </c>
     </row>
-    <row r="71" spans="1:57" ht="13.8">
+    <row r="71" spans="1:57" ht="14">
       <c r="A71" s="15" t="s">
         <v>51</v>
       </c>
@@ -13365,7 +13365,7 @@
         <v>57697.5</v>
       </c>
     </row>
-    <row r="72" spans="1:57" ht="13.8">
+    <row r="72" spans="1:57" ht="14">
       <c r="A72" s="15" t="s">
         <v>50</v>
       </c>
@@ -13538,7 +13538,7 @@
         <v>7567.8</v>
       </c>
     </row>
-    <row r="73" spans="1:57" ht="13.8">
+    <row r="73" spans="1:57" ht="14">
       <c r="A73" s="15" t="s">
         <v>49</v>
       </c>
@@ -13718,11 +13718,40 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="AB9:AC9"/>
-    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:BE3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:BE4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:BE5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:BE6"/>
+    <mergeCell ref="A7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:BE7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:AD8"/>
+    <mergeCell ref="AE8:AE10"/>
+    <mergeCell ref="AF8:AF10"/>
+    <mergeCell ref="AG8:AG10"/>
+    <mergeCell ref="AH8:AR8"/>
+    <mergeCell ref="AS8:AS10"/>
+    <mergeCell ref="AT8:AZ8"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="AL9:AL10"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="BA8:BA10"/>
+    <mergeCell ref="AY9:AZ9"/>
+    <mergeCell ref="AP9:AP10"/>
+    <mergeCell ref="AQ9:AQ10"/>
+    <mergeCell ref="AR9:AR10"/>
+    <mergeCell ref="AT9:AT10"/>
+    <mergeCell ref="AU9:AW9"/>
+    <mergeCell ref="AX9:AX10"/>
     <mergeCell ref="BB8:BB10"/>
     <mergeCell ref="BC8:BC10"/>
     <mergeCell ref="BD8:BD10"/>
@@ -13739,40 +13768,11 @@
     <mergeCell ref="T9:T10"/>
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="W9:W10"/>
-    <mergeCell ref="AH9:AH10"/>
-    <mergeCell ref="AI9:AK9"/>
-    <mergeCell ref="AL9:AL10"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="BA8:BA10"/>
-    <mergeCell ref="AY9:AZ9"/>
-    <mergeCell ref="AP9:AP10"/>
-    <mergeCell ref="AQ9:AQ10"/>
-    <mergeCell ref="AR9:AR10"/>
-    <mergeCell ref="AT9:AT10"/>
-    <mergeCell ref="AU9:AW9"/>
-    <mergeCell ref="AX9:AX10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:BE6"/>
-    <mergeCell ref="A7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="D7:BE7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J8:AD8"/>
-    <mergeCell ref="AE8:AE10"/>
-    <mergeCell ref="AF8:AF10"/>
-    <mergeCell ref="AG8:AG10"/>
-    <mergeCell ref="AH8:AR8"/>
-    <mergeCell ref="AS8:AS10"/>
-    <mergeCell ref="AT8:AZ8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:BE3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:BE4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:BE5"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="AB9:AC9"/>
+    <mergeCell ref="AD9:AD10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="http://localhost/OECDStat_Metadata/ShowMetadata.ashx?Dataset=TIM_2019_MAIN&amp;ShowOnWeb=true&amp;Lang=en" xr:uid="{3FEC89F7-2DF7-491F-AA22-C2D56987BE46}"/>
@@ -13798,7 +13798,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD357E6B-F64C-469A-93EB-8B897A89C3FF}">
   <dimension ref="A1:AK63"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="37" width="10.33203125" customWidth="1"/>
@@ -23222,324 +23222,324 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCCC9D3-CC94-48F2-9058-AA6BCF847F9B}">
   <dimension ref="A1:N76"/>
-  <sheetFormatPr defaultColWidth="6.33203125" defaultRowHeight="7.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.33203125" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="1" width="5.109375" style="64" customWidth="1"/>
-    <col min="2" max="2" width="48.21875" style="64" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" style="64" customWidth="1"/>
+    <col min="2" max="2" width="48.1640625" style="64" customWidth="1"/>
     <col min="3" max="14" width="9.33203125" style="64" customWidth="1"/>
     <col min="15" max="256" width="6.33203125" style="64"/>
-    <col min="257" max="257" width="5.109375" style="64" customWidth="1"/>
-    <col min="258" max="258" width="48.21875" style="64" customWidth="1"/>
+    <col min="257" max="257" width="5.1640625" style="64" customWidth="1"/>
+    <col min="258" max="258" width="48.1640625" style="64" customWidth="1"/>
     <col min="259" max="263" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="264" max="270" width="9.33203125" style="64" customWidth="1"/>
     <col min="271" max="512" width="6.33203125" style="64"/>
-    <col min="513" max="513" width="5.109375" style="64" customWidth="1"/>
-    <col min="514" max="514" width="48.21875" style="64" customWidth="1"/>
+    <col min="513" max="513" width="5.1640625" style="64" customWidth="1"/>
+    <col min="514" max="514" width="48.1640625" style="64" customWidth="1"/>
     <col min="515" max="519" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="520" max="526" width="9.33203125" style="64" customWidth="1"/>
     <col min="527" max="768" width="6.33203125" style="64"/>
-    <col min="769" max="769" width="5.109375" style="64" customWidth="1"/>
-    <col min="770" max="770" width="48.21875" style="64" customWidth="1"/>
+    <col min="769" max="769" width="5.1640625" style="64" customWidth="1"/>
+    <col min="770" max="770" width="48.1640625" style="64" customWidth="1"/>
     <col min="771" max="775" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="776" max="782" width="9.33203125" style="64" customWidth="1"/>
     <col min="783" max="1024" width="6.33203125" style="64"/>
-    <col min="1025" max="1025" width="5.109375" style="64" customWidth="1"/>
-    <col min="1026" max="1026" width="48.21875" style="64" customWidth="1"/>
+    <col min="1025" max="1025" width="5.1640625" style="64" customWidth="1"/>
+    <col min="1026" max="1026" width="48.1640625" style="64" customWidth="1"/>
     <col min="1027" max="1031" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="1032" max="1038" width="9.33203125" style="64" customWidth="1"/>
     <col min="1039" max="1280" width="6.33203125" style="64"/>
-    <col min="1281" max="1281" width="5.109375" style="64" customWidth="1"/>
-    <col min="1282" max="1282" width="48.21875" style="64" customWidth="1"/>
+    <col min="1281" max="1281" width="5.1640625" style="64" customWidth="1"/>
+    <col min="1282" max="1282" width="48.1640625" style="64" customWidth="1"/>
     <col min="1283" max="1287" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="1288" max="1294" width="9.33203125" style="64" customWidth="1"/>
     <col min="1295" max="1536" width="6.33203125" style="64"/>
-    <col min="1537" max="1537" width="5.109375" style="64" customWidth="1"/>
-    <col min="1538" max="1538" width="48.21875" style="64" customWidth="1"/>
+    <col min="1537" max="1537" width="5.1640625" style="64" customWidth="1"/>
+    <col min="1538" max="1538" width="48.1640625" style="64" customWidth="1"/>
     <col min="1539" max="1543" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="1544" max="1550" width="9.33203125" style="64" customWidth="1"/>
     <col min="1551" max="1792" width="6.33203125" style="64"/>
-    <col min="1793" max="1793" width="5.109375" style="64" customWidth="1"/>
-    <col min="1794" max="1794" width="48.21875" style="64" customWidth="1"/>
+    <col min="1793" max="1793" width="5.1640625" style="64" customWidth="1"/>
+    <col min="1794" max="1794" width="48.1640625" style="64" customWidth="1"/>
     <col min="1795" max="1799" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="1800" max="1806" width="9.33203125" style="64" customWidth="1"/>
     <col min="1807" max="2048" width="6.33203125" style="64"/>
-    <col min="2049" max="2049" width="5.109375" style="64" customWidth="1"/>
-    <col min="2050" max="2050" width="48.21875" style="64" customWidth="1"/>
+    <col min="2049" max="2049" width="5.1640625" style="64" customWidth="1"/>
+    <col min="2050" max="2050" width="48.1640625" style="64" customWidth="1"/>
     <col min="2051" max="2055" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="2056" max="2062" width="9.33203125" style="64" customWidth="1"/>
     <col min="2063" max="2304" width="6.33203125" style="64"/>
-    <col min="2305" max="2305" width="5.109375" style="64" customWidth="1"/>
-    <col min="2306" max="2306" width="48.21875" style="64" customWidth="1"/>
+    <col min="2305" max="2305" width="5.1640625" style="64" customWidth="1"/>
+    <col min="2306" max="2306" width="48.1640625" style="64" customWidth="1"/>
     <col min="2307" max="2311" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="2312" max="2318" width="9.33203125" style="64" customWidth="1"/>
     <col min="2319" max="2560" width="6.33203125" style="64"/>
-    <col min="2561" max="2561" width="5.109375" style="64" customWidth="1"/>
-    <col min="2562" max="2562" width="48.21875" style="64" customWidth="1"/>
+    <col min="2561" max="2561" width="5.1640625" style="64" customWidth="1"/>
+    <col min="2562" max="2562" width="48.1640625" style="64" customWidth="1"/>
     <col min="2563" max="2567" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="2568" max="2574" width="9.33203125" style="64" customWidth="1"/>
     <col min="2575" max="2816" width="6.33203125" style="64"/>
-    <col min="2817" max="2817" width="5.109375" style="64" customWidth="1"/>
-    <col min="2818" max="2818" width="48.21875" style="64" customWidth="1"/>
+    <col min="2817" max="2817" width="5.1640625" style="64" customWidth="1"/>
+    <col min="2818" max="2818" width="48.1640625" style="64" customWidth="1"/>
     <col min="2819" max="2823" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="2824" max="2830" width="9.33203125" style="64" customWidth="1"/>
     <col min="2831" max="3072" width="6.33203125" style="64"/>
-    <col min="3073" max="3073" width="5.109375" style="64" customWidth="1"/>
-    <col min="3074" max="3074" width="48.21875" style="64" customWidth="1"/>
+    <col min="3073" max="3073" width="5.1640625" style="64" customWidth="1"/>
+    <col min="3074" max="3074" width="48.1640625" style="64" customWidth="1"/>
     <col min="3075" max="3079" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="3080" max="3086" width="9.33203125" style="64" customWidth="1"/>
     <col min="3087" max="3328" width="6.33203125" style="64"/>
-    <col min="3329" max="3329" width="5.109375" style="64" customWidth="1"/>
-    <col min="3330" max="3330" width="48.21875" style="64" customWidth="1"/>
+    <col min="3329" max="3329" width="5.1640625" style="64" customWidth="1"/>
+    <col min="3330" max="3330" width="48.1640625" style="64" customWidth="1"/>
     <col min="3331" max="3335" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="3336" max="3342" width="9.33203125" style="64" customWidth="1"/>
     <col min="3343" max="3584" width="6.33203125" style="64"/>
-    <col min="3585" max="3585" width="5.109375" style="64" customWidth="1"/>
-    <col min="3586" max="3586" width="48.21875" style="64" customWidth="1"/>
+    <col min="3585" max="3585" width="5.1640625" style="64" customWidth="1"/>
+    <col min="3586" max="3586" width="48.1640625" style="64" customWidth="1"/>
     <col min="3587" max="3591" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="3592" max="3598" width="9.33203125" style="64" customWidth="1"/>
     <col min="3599" max="3840" width="6.33203125" style="64"/>
-    <col min="3841" max="3841" width="5.109375" style="64" customWidth="1"/>
-    <col min="3842" max="3842" width="48.21875" style="64" customWidth="1"/>
+    <col min="3841" max="3841" width="5.1640625" style="64" customWidth="1"/>
+    <col min="3842" max="3842" width="48.1640625" style="64" customWidth="1"/>
     <col min="3843" max="3847" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="3848" max="3854" width="9.33203125" style="64" customWidth="1"/>
     <col min="3855" max="4096" width="6.33203125" style="64"/>
-    <col min="4097" max="4097" width="5.109375" style="64" customWidth="1"/>
-    <col min="4098" max="4098" width="48.21875" style="64" customWidth="1"/>
+    <col min="4097" max="4097" width="5.1640625" style="64" customWidth="1"/>
+    <col min="4098" max="4098" width="48.1640625" style="64" customWidth="1"/>
     <col min="4099" max="4103" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="4104" max="4110" width="9.33203125" style="64" customWidth="1"/>
     <col min="4111" max="4352" width="6.33203125" style="64"/>
-    <col min="4353" max="4353" width="5.109375" style="64" customWidth="1"/>
-    <col min="4354" max="4354" width="48.21875" style="64" customWidth="1"/>
+    <col min="4353" max="4353" width="5.1640625" style="64" customWidth="1"/>
+    <col min="4354" max="4354" width="48.1640625" style="64" customWidth="1"/>
     <col min="4355" max="4359" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="4360" max="4366" width="9.33203125" style="64" customWidth="1"/>
     <col min="4367" max="4608" width="6.33203125" style="64"/>
-    <col min="4609" max="4609" width="5.109375" style="64" customWidth="1"/>
-    <col min="4610" max="4610" width="48.21875" style="64" customWidth="1"/>
+    <col min="4609" max="4609" width="5.1640625" style="64" customWidth="1"/>
+    <col min="4610" max="4610" width="48.1640625" style="64" customWidth="1"/>
     <col min="4611" max="4615" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="4616" max="4622" width="9.33203125" style="64" customWidth="1"/>
     <col min="4623" max="4864" width="6.33203125" style="64"/>
-    <col min="4865" max="4865" width="5.109375" style="64" customWidth="1"/>
-    <col min="4866" max="4866" width="48.21875" style="64" customWidth="1"/>
+    <col min="4865" max="4865" width="5.1640625" style="64" customWidth="1"/>
+    <col min="4866" max="4866" width="48.1640625" style="64" customWidth="1"/>
     <col min="4867" max="4871" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="4872" max="4878" width="9.33203125" style="64" customWidth="1"/>
     <col min="4879" max="5120" width="6.33203125" style="64"/>
-    <col min="5121" max="5121" width="5.109375" style="64" customWidth="1"/>
-    <col min="5122" max="5122" width="48.21875" style="64" customWidth="1"/>
+    <col min="5121" max="5121" width="5.1640625" style="64" customWidth="1"/>
+    <col min="5122" max="5122" width="48.1640625" style="64" customWidth="1"/>
     <col min="5123" max="5127" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="5128" max="5134" width="9.33203125" style="64" customWidth="1"/>
     <col min="5135" max="5376" width="6.33203125" style="64"/>
-    <col min="5377" max="5377" width="5.109375" style="64" customWidth="1"/>
-    <col min="5378" max="5378" width="48.21875" style="64" customWidth="1"/>
+    <col min="5377" max="5377" width="5.1640625" style="64" customWidth="1"/>
+    <col min="5378" max="5378" width="48.1640625" style="64" customWidth="1"/>
     <col min="5379" max="5383" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="5384" max="5390" width="9.33203125" style="64" customWidth="1"/>
     <col min="5391" max="5632" width="6.33203125" style="64"/>
-    <col min="5633" max="5633" width="5.109375" style="64" customWidth="1"/>
-    <col min="5634" max="5634" width="48.21875" style="64" customWidth="1"/>
+    <col min="5633" max="5633" width="5.1640625" style="64" customWidth="1"/>
+    <col min="5634" max="5634" width="48.1640625" style="64" customWidth="1"/>
     <col min="5635" max="5639" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="5640" max="5646" width="9.33203125" style="64" customWidth="1"/>
     <col min="5647" max="5888" width="6.33203125" style="64"/>
-    <col min="5889" max="5889" width="5.109375" style="64" customWidth="1"/>
-    <col min="5890" max="5890" width="48.21875" style="64" customWidth="1"/>
+    <col min="5889" max="5889" width="5.1640625" style="64" customWidth="1"/>
+    <col min="5890" max="5890" width="48.1640625" style="64" customWidth="1"/>
     <col min="5891" max="5895" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="5896" max="5902" width="9.33203125" style="64" customWidth="1"/>
     <col min="5903" max="6144" width="6.33203125" style="64"/>
-    <col min="6145" max="6145" width="5.109375" style="64" customWidth="1"/>
-    <col min="6146" max="6146" width="48.21875" style="64" customWidth="1"/>
+    <col min="6145" max="6145" width="5.1640625" style="64" customWidth="1"/>
+    <col min="6146" max="6146" width="48.1640625" style="64" customWidth="1"/>
     <col min="6147" max="6151" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="6152" max="6158" width="9.33203125" style="64" customWidth="1"/>
     <col min="6159" max="6400" width="6.33203125" style="64"/>
-    <col min="6401" max="6401" width="5.109375" style="64" customWidth="1"/>
-    <col min="6402" max="6402" width="48.21875" style="64" customWidth="1"/>
+    <col min="6401" max="6401" width="5.1640625" style="64" customWidth="1"/>
+    <col min="6402" max="6402" width="48.1640625" style="64" customWidth="1"/>
     <col min="6403" max="6407" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="6408" max="6414" width="9.33203125" style="64" customWidth="1"/>
     <col min="6415" max="6656" width="6.33203125" style="64"/>
-    <col min="6657" max="6657" width="5.109375" style="64" customWidth="1"/>
-    <col min="6658" max="6658" width="48.21875" style="64" customWidth="1"/>
+    <col min="6657" max="6657" width="5.1640625" style="64" customWidth="1"/>
+    <col min="6658" max="6658" width="48.1640625" style="64" customWidth="1"/>
     <col min="6659" max="6663" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="6664" max="6670" width="9.33203125" style="64" customWidth="1"/>
     <col min="6671" max="6912" width="6.33203125" style="64"/>
-    <col min="6913" max="6913" width="5.109375" style="64" customWidth="1"/>
-    <col min="6914" max="6914" width="48.21875" style="64" customWidth="1"/>
+    <col min="6913" max="6913" width="5.1640625" style="64" customWidth="1"/>
+    <col min="6914" max="6914" width="48.1640625" style="64" customWidth="1"/>
     <col min="6915" max="6919" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="6920" max="6926" width="9.33203125" style="64" customWidth="1"/>
     <col min="6927" max="7168" width="6.33203125" style="64"/>
-    <col min="7169" max="7169" width="5.109375" style="64" customWidth="1"/>
-    <col min="7170" max="7170" width="48.21875" style="64" customWidth="1"/>
+    <col min="7169" max="7169" width="5.1640625" style="64" customWidth="1"/>
+    <col min="7170" max="7170" width="48.1640625" style="64" customWidth="1"/>
     <col min="7171" max="7175" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="7176" max="7182" width="9.33203125" style="64" customWidth="1"/>
     <col min="7183" max="7424" width="6.33203125" style="64"/>
-    <col min="7425" max="7425" width="5.109375" style="64" customWidth="1"/>
-    <col min="7426" max="7426" width="48.21875" style="64" customWidth="1"/>
+    <col min="7425" max="7425" width="5.1640625" style="64" customWidth="1"/>
+    <col min="7426" max="7426" width="48.1640625" style="64" customWidth="1"/>
     <col min="7427" max="7431" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="7432" max="7438" width="9.33203125" style="64" customWidth="1"/>
     <col min="7439" max="7680" width="6.33203125" style="64"/>
-    <col min="7681" max="7681" width="5.109375" style="64" customWidth="1"/>
-    <col min="7682" max="7682" width="48.21875" style="64" customWidth="1"/>
+    <col min="7681" max="7681" width="5.1640625" style="64" customWidth="1"/>
+    <col min="7682" max="7682" width="48.1640625" style="64" customWidth="1"/>
     <col min="7683" max="7687" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="7688" max="7694" width="9.33203125" style="64" customWidth="1"/>
     <col min="7695" max="7936" width="6.33203125" style="64"/>
-    <col min="7937" max="7937" width="5.109375" style="64" customWidth="1"/>
-    <col min="7938" max="7938" width="48.21875" style="64" customWidth="1"/>
+    <col min="7937" max="7937" width="5.1640625" style="64" customWidth="1"/>
+    <col min="7938" max="7938" width="48.1640625" style="64" customWidth="1"/>
     <col min="7939" max="7943" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="7944" max="7950" width="9.33203125" style="64" customWidth="1"/>
     <col min="7951" max="8192" width="6.33203125" style="64"/>
-    <col min="8193" max="8193" width="5.109375" style="64" customWidth="1"/>
-    <col min="8194" max="8194" width="48.21875" style="64" customWidth="1"/>
+    <col min="8193" max="8193" width="5.1640625" style="64" customWidth="1"/>
+    <col min="8194" max="8194" width="48.1640625" style="64" customWidth="1"/>
     <col min="8195" max="8199" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="8200" max="8206" width="9.33203125" style="64" customWidth="1"/>
     <col min="8207" max="8448" width="6.33203125" style="64"/>
-    <col min="8449" max="8449" width="5.109375" style="64" customWidth="1"/>
-    <col min="8450" max="8450" width="48.21875" style="64" customWidth="1"/>
+    <col min="8449" max="8449" width="5.1640625" style="64" customWidth="1"/>
+    <col min="8450" max="8450" width="48.1640625" style="64" customWidth="1"/>
     <col min="8451" max="8455" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="8456" max="8462" width="9.33203125" style="64" customWidth="1"/>
     <col min="8463" max="8704" width="6.33203125" style="64"/>
-    <col min="8705" max="8705" width="5.109375" style="64" customWidth="1"/>
-    <col min="8706" max="8706" width="48.21875" style="64" customWidth="1"/>
+    <col min="8705" max="8705" width="5.1640625" style="64" customWidth="1"/>
+    <col min="8706" max="8706" width="48.1640625" style="64" customWidth="1"/>
     <col min="8707" max="8711" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="8712" max="8718" width="9.33203125" style="64" customWidth="1"/>
     <col min="8719" max="8960" width="6.33203125" style="64"/>
-    <col min="8961" max="8961" width="5.109375" style="64" customWidth="1"/>
-    <col min="8962" max="8962" width="48.21875" style="64" customWidth="1"/>
+    <col min="8961" max="8961" width="5.1640625" style="64" customWidth="1"/>
+    <col min="8962" max="8962" width="48.1640625" style="64" customWidth="1"/>
     <col min="8963" max="8967" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="8968" max="8974" width="9.33203125" style="64" customWidth="1"/>
     <col min="8975" max="9216" width="6.33203125" style="64"/>
-    <col min="9217" max="9217" width="5.109375" style="64" customWidth="1"/>
-    <col min="9218" max="9218" width="48.21875" style="64" customWidth="1"/>
+    <col min="9217" max="9217" width="5.1640625" style="64" customWidth="1"/>
+    <col min="9218" max="9218" width="48.1640625" style="64" customWidth="1"/>
     <col min="9219" max="9223" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="9224" max="9230" width="9.33203125" style="64" customWidth="1"/>
     <col min="9231" max="9472" width="6.33203125" style="64"/>
-    <col min="9473" max="9473" width="5.109375" style="64" customWidth="1"/>
-    <col min="9474" max="9474" width="48.21875" style="64" customWidth="1"/>
+    <col min="9473" max="9473" width="5.1640625" style="64" customWidth="1"/>
+    <col min="9474" max="9474" width="48.1640625" style="64" customWidth="1"/>
     <col min="9475" max="9479" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="9480" max="9486" width="9.33203125" style="64" customWidth="1"/>
     <col min="9487" max="9728" width="6.33203125" style="64"/>
-    <col min="9729" max="9729" width="5.109375" style="64" customWidth="1"/>
-    <col min="9730" max="9730" width="48.21875" style="64" customWidth="1"/>
+    <col min="9729" max="9729" width="5.1640625" style="64" customWidth="1"/>
+    <col min="9730" max="9730" width="48.1640625" style="64" customWidth="1"/>
     <col min="9731" max="9735" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="9736" max="9742" width="9.33203125" style="64" customWidth="1"/>
     <col min="9743" max="9984" width="6.33203125" style="64"/>
-    <col min="9985" max="9985" width="5.109375" style="64" customWidth="1"/>
-    <col min="9986" max="9986" width="48.21875" style="64" customWidth="1"/>
+    <col min="9985" max="9985" width="5.1640625" style="64" customWidth="1"/>
+    <col min="9986" max="9986" width="48.1640625" style="64" customWidth="1"/>
     <col min="9987" max="9991" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="9992" max="9998" width="9.33203125" style="64" customWidth="1"/>
     <col min="9999" max="10240" width="6.33203125" style="64"/>
-    <col min="10241" max="10241" width="5.109375" style="64" customWidth="1"/>
-    <col min="10242" max="10242" width="48.21875" style="64" customWidth="1"/>
+    <col min="10241" max="10241" width="5.1640625" style="64" customWidth="1"/>
+    <col min="10242" max="10242" width="48.1640625" style="64" customWidth="1"/>
     <col min="10243" max="10247" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="10248" max="10254" width="9.33203125" style="64" customWidth="1"/>
     <col min="10255" max="10496" width="6.33203125" style="64"/>
-    <col min="10497" max="10497" width="5.109375" style="64" customWidth="1"/>
-    <col min="10498" max="10498" width="48.21875" style="64" customWidth="1"/>
+    <col min="10497" max="10497" width="5.1640625" style="64" customWidth="1"/>
+    <col min="10498" max="10498" width="48.1640625" style="64" customWidth="1"/>
     <col min="10499" max="10503" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="10504" max="10510" width="9.33203125" style="64" customWidth="1"/>
     <col min="10511" max="10752" width="6.33203125" style="64"/>
-    <col min="10753" max="10753" width="5.109375" style="64" customWidth="1"/>
-    <col min="10754" max="10754" width="48.21875" style="64" customWidth="1"/>
+    <col min="10753" max="10753" width="5.1640625" style="64" customWidth="1"/>
+    <col min="10754" max="10754" width="48.1640625" style="64" customWidth="1"/>
     <col min="10755" max="10759" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="10760" max="10766" width="9.33203125" style="64" customWidth="1"/>
     <col min="10767" max="11008" width="6.33203125" style="64"/>
-    <col min="11009" max="11009" width="5.109375" style="64" customWidth="1"/>
-    <col min="11010" max="11010" width="48.21875" style="64" customWidth="1"/>
+    <col min="11009" max="11009" width="5.1640625" style="64" customWidth="1"/>
+    <col min="11010" max="11010" width="48.1640625" style="64" customWidth="1"/>
     <col min="11011" max="11015" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="11016" max="11022" width="9.33203125" style="64" customWidth="1"/>
     <col min="11023" max="11264" width="6.33203125" style="64"/>
-    <col min="11265" max="11265" width="5.109375" style="64" customWidth="1"/>
-    <col min="11266" max="11266" width="48.21875" style="64" customWidth="1"/>
+    <col min="11265" max="11265" width="5.1640625" style="64" customWidth="1"/>
+    <col min="11266" max="11266" width="48.1640625" style="64" customWidth="1"/>
     <col min="11267" max="11271" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="11272" max="11278" width="9.33203125" style="64" customWidth="1"/>
     <col min="11279" max="11520" width="6.33203125" style="64"/>
-    <col min="11521" max="11521" width="5.109375" style="64" customWidth="1"/>
-    <col min="11522" max="11522" width="48.21875" style="64" customWidth="1"/>
+    <col min="11521" max="11521" width="5.1640625" style="64" customWidth="1"/>
+    <col min="11522" max="11522" width="48.1640625" style="64" customWidth="1"/>
     <col min="11523" max="11527" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="11528" max="11534" width="9.33203125" style="64" customWidth="1"/>
     <col min="11535" max="11776" width="6.33203125" style="64"/>
-    <col min="11777" max="11777" width="5.109375" style="64" customWidth="1"/>
-    <col min="11778" max="11778" width="48.21875" style="64" customWidth="1"/>
+    <col min="11777" max="11777" width="5.1640625" style="64" customWidth="1"/>
+    <col min="11778" max="11778" width="48.1640625" style="64" customWidth="1"/>
     <col min="11779" max="11783" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="11784" max="11790" width="9.33203125" style="64" customWidth="1"/>
     <col min="11791" max="12032" width="6.33203125" style="64"/>
-    <col min="12033" max="12033" width="5.109375" style="64" customWidth="1"/>
-    <col min="12034" max="12034" width="48.21875" style="64" customWidth="1"/>
+    <col min="12033" max="12033" width="5.1640625" style="64" customWidth="1"/>
+    <col min="12034" max="12034" width="48.1640625" style="64" customWidth="1"/>
     <col min="12035" max="12039" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="12040" max="12046" width="9.33203125" style="64" customWidth="1"/>
     <col min="12047" max="12288" width="6.33203125" style="64"/>
-    <col min="12289" max="12289" width="5.109375" style="64" customWidth="1"/>
-    <col min="12290" max="12290" width="48.21875" style="64" customWidth="1"/>
+    <col min="12289" max="12289" width="5.1640625" style="64" customWidth="1"/>
+    <col min="12290" max="12290" width="48.1640625" style="64" customWidth="1"/>
     <col min="12291" max="12295" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="12296" max="12302" width="9.33203125" style="64" customWidth="1"/>
     <col min="12303" max="12544" width="6.33203125" style="64"/>
-    <col min="12545" max="12545" width="5.109375" style="64" customWidth="1"/>
-    <col min="12546" max="12546" width="48.21875" style="64" customWidth="1"/>
+    <col min="12545" max="12545" width="5.1640625" style="64" customWidth="1"/>
+    <col min="12546" max="12546" width="48.1640625" style="64" customWidth="1"/>
     <col min="12547" max="12551" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="12552" max="12558" width="9.33203125" style="64" customWidth="1"/>
     <col min="12559" max="12800" width="6.33203125" style="64"/>
-    <col min="12801" max="12801" width="5.109375" style="64" customWidth="1"/>
-    <col min="12802" max="12802" width="48.21875" style="64" customWidth="1"/>
+    <col min="12801" max="12801" width="5.1640625" style="64" customWidth="1"/>
+    <col min="12802" max="12802" width="48.1640625" style="64" customWidth="1"/>
     <col min="12803" max="12807" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="12808" max="12814" width="9.33203125" style="64" customWidth="1"/>
     <col min="12815" max="13056" width="6.33203125" style="64"/>
-    <col min="13057" max="13057" width="5.109375" style="64" customWidth="1"/>
-    <col min="13058" max="13058" width="48.21875" style="64" customWidth="1"/>
+    <col min="13057" max="13057" width="5.1640625" style="64" customWidth="1"/>
+    <col min="13058" max="13058" width="48.1640625" style="64" customWidth="1"/>
     <col min="13059" max="13063" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="13064" max="13070" width="9.33203125" style="64" customWidth="1"/>
     <col min="13071" max="13312" width="6.33203125" style="64"/>
-    <col min="13313" max="13313" width="5.109375" style="64" customWidth="1"/>
-    <col min="13314" max="13314" width="48.21875" style="64" customWidth="1"/>
+    <col min="13313" max="13313" width="5.1640625" style="64" customWidth="1"/>
+    <col min="13314" max="13314" width="48.1640625" style="64" customWidth="1"/>
     <col min="13315" max="13319" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="13320" max="13326" width="9.33203125" style="64" customWidth="1"/>
     <col min="13327" max="13568" width="6.33203125" style="64"/>
-    <col min="13569" max="13569" width="5.109375" style="64" customWidth="1"/>
-    <col min="13570" max="13570" width="48.21875" style="64" customWidth="1"/>
+    <col min="13569" max="13569" width="5.1640625" style="64" customWidth="1"/>
+    <col min="13570" max="13570" width="48.1640625" style="64" customWidth="1"/>
     <col min="13571" max="13575" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="13576" max="13582" width="9.33203125" style="64" customWidth="1"/>
     <col min="13583" max="13824" width="6.33203125" style="64"/>
-    <col min="13825" max="13825" width="5.109375" style="64" customWidth="1"/>
-    <col min="13826" max="13826" width="48.21875" style="64" customWidth="1"/>
+    <col min="13825" max="13825" width="5.1640625" style="64" customWidth="1"/>
+    <col min="13826" max="13826" width="48.1640625" style="64" customWidth="1"/>
     <col min="13827" max="13831" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="13832" max="13838" width="9.33203125" style="64" customWidth="1"/>
     <col min="13839" max="14080" width="6.33203125" style="64"/>
-    <col min="14081" max="14081" width="5.109375" style="64" customWidth="1"/>
-    <col min="14082" max="14082" width="48.21875" style="64" customWidth="1"/>
+    <col min="14081" max="14081" width="5.1640625" style="64" customWidth="1"/>
+    <col min="14082" max="14082" width="48.1640625" style="64" customWidth="1"/>
     <col min="14083" max="14087" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="14088" max="14094" width="9.33203125" style="64" customWidth="1"/>
     <col min="14095" max="14336" width="6.33203125" style="64"/>
-    <col min="14337" max="14337" width="5.109375" style="64" customWidth="1"/>
-    <col min="14338" max="14338" width="48.21875" style="64" customWidth="1"/>
+    <col min="14337" max="14337" width="5.1640625" style="64" customWidth="1"/>
+    <col min="14338" max="14338" width="48.1640625" style="64" customWidth="1"/>
     <col min="14339" max="14343" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="14344" max="14350" width="9.33203125" style="64" customWidth="1"/>
     <col min="14351" max="14592" width="6.33203125" style="64"/>
-    <col min="14593" max="14593" width="5.109375" style="64" customWidth="1"/>
-    <col min="14594" max="14594" width="48.21875" style="64" customWidth="1"/>
+    <col min="14593" max="14593" width="5.1640625" style="64" customWidth="1"/>
+    <col min="14594" max="14594" width="48.1640625" style="64" customWidth="1"/>
     <col min="14595" max="14599" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="14600" max="14606" width="9.33203125" style="64" customWidth="1"/>
     <col min="14607" max="14848" width="6.33203125" style="64"/>
-    <col min="14849" max="14849" width="5.109375" style="64" customWidth="1"/>
-    <col min="14850" max="14850" width="48.21875" style="64" customWidth="1"/>
+    <col min="14849" max="14849" width="5.1640625" style="64" customWidth="1"/>
+    <col min="14850" max="14850" width="48.1640625" style="64" customWidth="1"/>
     <col min="14851" max="14855" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="14856" max="14862" width="9.33203125" style="64" customWidth="1"/>
     <col min="14863" max="15104" width="6.33203125" style="64"/>
-    <col min="15105" max="15105" width="5.109375" style="64" customWidth="1"/>
-    <col min="15106" max="15106" width="48.21875" style="64" customWidth="1"/>
+    <col min="15105" max="15105" width="5.1640625" style="64" customWidth="1"/>
+    <col min="15106" max="15106" width="48.1640625" style="64" customWidth="1"/>
     <col min="15107" max="15111" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="15112" max="15118" width="9.33203125" style="64" customWidth="1"/>
     <col min="15119" max="15360" width="6.33203125" style="64"/>
-    <col min="15361" max="15361" width="5.109375" style="64" customWidth="1"/>
-    <col min="15362" max="15362" width="48.21875" style="64" customWidth="1"/>
+    <col min="15361" max="15361" width="5.1640625" style="64" customWidth="1"/>
+    <col min="15362" max="15362" width="48.1640625" style="64" customWidth="1"/>
     <col min="15363" max="15367" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="15368" max="15374" width="9.33203125" style="64" customWidth="1"/>
     <col min="15375" max="15616" width="6.33203125" style="64"/>
-    <col min="15617" max="15617" width="5.109375" style="64" customWidth="1"/>
-    <col min="15618" max="15618" width="48.21875" style="64" customWidth="1"/>
+    <col min="15617" max="15617" width="5.1640625" style="64" customWidth="1"/>
+    <col min="15618" max="15618" width="48.1640625" style="64" customWidth="1"/>
     <col min="15619" max="15623" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="15624" max="15630" width="9.33203125" style="64" customWidth="1"/>
     <col min="15631" max="15872" width="6.33203125" style="64"/>
-    <col min="15873" max="15873" width="5.109375" style="64" customWidth="1"/>
-    <col min="15874" max="15874" width="48.21875" style="64" customWidth="1"/>
+    <col min="15873" max="15873" width="5.1640625" style="64" customWidth="1"/>
+    <col min="15874" max="15874" width="48.1640625" style="64" customWidth="1"/>
     <col min="15875" max="15879" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="15880" max="15886" width="9.33203125" style="64" customWidth="1"/>
     <col min="15887" max="16128" width="6.33203125" style="64"/>
-    <col min="16129" max="16129" width="5.109375" style="64" customWidth="1"/>
-    <col min="16130" max="16130" width="48.21875" style="64" customWidth="1"/>
+    <col min="16129" max="16129" width="5.1640625" style="64" customWidth="1"/>
+    <col min="16130" max="16130" width="48.1640625" style="64" customWidth="1"/>
     <col min="16131" max="16135" width="0" style="64" hidden="1" customWidth="1"/>
     <col min="16136" max="16142" width="9.33203125" style="64" customWidth="1"/>
     <col min="16143" max="16384" width="6.33203125" style="64"/>
@@ -26679,7 +26679,7 @@
         <v>5633396</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="5.0999999999999996" customHeight="1">
+    <row r="75" spans="1:14" ht="5" customHeight="1">
       <c r="A75" s="69"/>
       <c r="B75" s="70"/>
       <c r="C75" s="71"/>
@@ -26695,7 +26695,7 @@
       <c r="M75" s="71"/>
       <c r="N75" s="71"/>
     </row>
-    <row r="76" spans="1:14" ht="13.2" customHeight="1">
+    <row r="76" spans="1:14" ht="13.25" customHeight="1">
       <c r="A76" s="72" t="s">
         <v>300</v>
       </c>
@@ -26718,24 +26718,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1E095F-2FE0-4341-A3C8-1B74B91EB662}">
   <dimension ref="A1:S443"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.33203125" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="40.109375" customWidth="1"/>
+    <col min="3" max="3" width="40.1640625" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
-    <col min="7" max="9" width="20.88671875" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="11" max="11" width="23.5" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
     <col min="13" max="13" width="20.33203125" customWidth="1"/>
-    <col min="14" max="15" width="18.44140625" customWidth="1"/>
+    <col min="14" max="15" width="18.5" customWidth="1"/>
     <col min="16" max="16" width="23" customWidth="1"/>
-    <col min="17" max="17" width="20.88671875" customWidth="1"/>
-    <col min="18" max="18" width="19.109375" customWidth="1"/>
-    <col min="19" max="19" width="16.5546875" customWidth="1"/>
+    <col min="17" max="17" width="20.83203125" customWidth="1"/>
+    <col min="18" max="18" width="19.1640625" customWidth="1"/>
+    <col min="19" max="19" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -26748,7 +26748,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="24" customFormat="1" ht="29.4" thickBot="1">
+    <row r="3" spans="1:19" s="24" customFormat="1" ht="33" thickBot="1">
       <c r="A3" s="31" t="s">
         <v>206</v>
       </c>
@@ -26807,7 +26807,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickTop="1">
+    <row r="4" spans="1:19" ht="16" thickTop="1">
       <c r="A4" s="26" t="s">
         <v>227</v>
       </c>
@@ -28804,13 +28804,13 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="26" width="10.109375" customWidth="1"/>
-    <col min="27" max="27" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="2" max="26" width="10.1640625" customWidth="1"/>
+    <col min="27" max="27" width="13.83203125" customWidth="1"/>
     <col min="28" max="28" width="10.6640625" customWidth="1"/>
-    <col min="29" max="43" width="10.109375" customWidth="1"/>
+    <col min="29" max="43" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="4" customFormat="1">
@@ -28944,7 +28944,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="15" thickBot="1">
+    <row r="2" spans="1:43" ht="16" thickBot="1">
       <c r="A2" t="str">
         <f>'Filtered OECD Data'!A41</f>
         <v>BRA: Brazil</v>
